--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:00</t>
+    <t xml:space="preserve">2026-09-10 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:12</t>
+    <t xml:space="preserve">2026-09-12 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:24</t>
+    <t xml:space="preserve">2026-09-23 23:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:53</t>
+    <t xml:space="preserve">2026-10-02 15:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
@@ -120,10 +120,10 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Álamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Alto Biobío</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:54</t>
+    <t xml:space="preserve">2026-10-04 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:34</t>
+    <t xml:space="preserve">2026-10-05 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
